--- a/telegram_profiles_test.xlsx
+++ b/telegram_profiles_test.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,14 +424,14 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Телефон</t>
+          <t>Username</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>3Dpoint Центр 3D-печати</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -439,7 +439,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aleksandr</t>
+          <t>A NAZARYAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -447,7 +447,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Aleksander25RU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -455,7 +455,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alexey Shipov</t>
+          <t>Aleksandra</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -463,15 +463,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alina</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>Alena B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>@le_broan</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Anton Smelyantsev</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -479,15 +483,19 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Denis Shevсhenko</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>Alex Ivan</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>@Alexis78spb</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Alex PR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -495,7 +503,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JuliaB</t>
+          <t>Alexey</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -503,7 +511,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Larisa</t>
+          <t>Alexey Prudnikov</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -511,23 +519,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mari</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>Alexey Sergeevich</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>@Alexey_Sergeevich_EKB</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mark | Лиды из TG/MAX</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>Alexey Shipov</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>@alekseyshipov</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>Alexmp</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -535,7 +551,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T G</t>
+          <t>Alina</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -543,10 +559,54 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tatyana | Главная по Фиолетовому WB</t>
+          <t>Alla Vasina</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Alsu</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>@Soushka</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AnBel</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Anastasiya S</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Andre</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Anika</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
